--- a/out/sample.xlsx
+++ b/out/sample.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="People" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Demo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -441,37 +441,122 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alice</t>
+          <t>山田太郎</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>初回</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bob</t>
+          <t>鈴木花子</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Osaka</t>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>金額が空欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>980</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>名前が空欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>佐藤健</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2024/09/04</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>日付がスラッシュ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>高橋優</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>日付が空欄</t>
         </is>
       </c>
     </row>
